--- a/results/job_matches_2026-06-01.xlsx
+++ b/results/job_matches_2026-06-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer</t>
+          <t>MS Server/Networking</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>La Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ebbbc1d7b8af0a</t>
+          <t>https://www.indeed.com/viewjob?jk=29bfb74f7babb87c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. SaaS Solutions Architect</t>
+          <t>Data Architect - C2H - Onsite</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Peloton</t>
+          <t>TEEMA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4058b3adc556b797</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b7749106eebc9f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MS Server/Networking</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>La Mesa, CA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29bfb74f7babb87c</t>
+          <t>https://www.indeed.com/viewjob?jk=9e1fdd788472d792</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,322 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e1fdd788472d792</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Data Engineering</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>DoorDash</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b0e08e23d0eaf7fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Software Engineer II, Data Engineering</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>DoorDash</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cc30e0ac9bbb52ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>DoorDash</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Redshift, S3, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f50dd3b28c07a04c</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer, Shield</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Box</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Redwood City, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=27d59ed7af29cac4</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Solutions Integration Engineer IV</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Samsara</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=865b851048dc7b7f</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Search Relevance</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Box</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Redwood City, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, ETL, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=46e11d1a4c8f8f51</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Applications Engineer, Full Stack - People</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>DoorDash</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, Cassandra, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d67500eca1ae208b</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior Backend Software Engineer | Achievements &amp; Gamification</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Wellhub</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AWS, SNS, RDS, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL, Git</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fa0b96826660e4c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>AI Software Engineer (Vehicle Engineering)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>SpaceX</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Hawthorne, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RDS, Scala, PostgreSQL, MLOps, MLflow, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ae57e531c0d4208e</t>
+          <t>https://www.indeed.com/viewjob?jk=c3a65fdc259b09f3</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-01.xlsx
+++ b/results/job_matches_2026-06-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,87 +468,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MS Server/Networking</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Block Labs</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>La Mesa, CA, US USA</t>
+          <t>Malta, MT, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.9</v>
+        <v>18.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29bfb74f7babb87c</t>
+          <t>https://www.indeed.com/viewjob?jk=a8521c97662c0b57</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Architect - C2H - Onsite</t>
+          <t>MS Server/Networking</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>La Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b7749106eebc9f</t>
+          <t>https://www.indeed.com/viewjob?jk=29bfb74f7babb87c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Architect - C2H - Onsite</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>TEEMA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,52 +556,192 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e1fdd788472d792</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b7749106eebc9f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>William Blair &amp; Company</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03c04b4f9272c367</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SYSTECH USA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Glendale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c3a65fdc259b09f3</t>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e1fdd788472d792</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Material Bank</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Boca Raton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a125832a9faf2b6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Material Bank</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13f4639de61892c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Material Bank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aaf0998b173a8e22</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-01.xlsx
+++ b/results/job_matches_2026-06-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Block Labs</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Malta, MT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, BigQuery, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8521c97662c0b57</t>
+          <t>https://www.indeed.com/viewjob?jk=d8cb8e3e7f036669</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MS Server/Networking</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Block Labs</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>La Mesa, CA, US USA</t>
+          <t>Malta, MT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.9</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29bfb74f7babb87c</t>
+          <t>https://www.indeed.com/viewjob?jk=a8521c97662c0b57</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Architect - C2H - Onsite</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.2</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Hadoop</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b7749106eebc9f</t>
+          <t>https://www.indeed.com/viewjob?jk=727aba117da7b7a0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>AWS Kinesis Developer – R01565561</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>William Blair &amp; Company</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, Kinesis, Athena, S3, SQS, API Gateway, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c04b4f9272c367</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b01bb5faaa172a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Healthcare Integration Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.2</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e1fdd788472d792</t>
+          <t>https://www.indeed.com/viewjob?jk=3653f445e14812b8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Material Bank</t>
+          <t>SmartTIX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.4</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a125832a9faf2b6d</t>
+          <t>https://www.indeed.com/viewjob?jk=a65fe6b467bcebd9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Material Bank</t>
+          <t>Edgewater Federal Solutions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.4</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,42 +706,987 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f4639de61892c3</t>
+          <t>https://www.indeed.com/viewjob?jk=db0719f5d865d28c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>The Evolvers Group</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8263a31ade65f67d</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Informatica Product Owner - Remote</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>The Jackson Laboratory</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bar Harbor, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db23110a8baa26ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Informatica Product Owner - Remote</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>The Jackson Laboratory</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f22eadc10f98f86e</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Informatica Product Owner - Remote</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>The Jackson Laboratory</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Farmington, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc73b585f3756066</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Informatica Product Owner - Remote</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>The Jackson Laboratory</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Alachua, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=031cba0efbfb272c</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Informatica Product Owner - Remote</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>The Jackson Laboratory</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Portland, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=356fb2d131354301</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Intern</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Copart, Inc</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e70e856c1968e4a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SkySlope</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3139e590b6a0719</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Data Architect - C2H - Onsite</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TEEMA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Flower Mound, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8b7749106eebc9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>William Blair &amp; Company</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03c04b4f9272c367</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Apollo Technology Solutions LLC</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Mechanicsburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b20eb19409e2893</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineer (Co-op)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ribbon Communications</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Westford, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Hadoop, HDFS, Impala, Scala, Kafka, NoSQL, ETL</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a073e33a9128dc9</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Paramount</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3a65fdc259b09f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Python Developer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, ETL, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d60d1f21a4e182da</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d74fea61e0c268af</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Brotherhood Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Fort Wayne, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ae07d8ce5e9b6c72</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Epsilon</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, NoSQL</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55697a169692173b</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Solutions Engineer(Python/Airflow)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>EDB</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ebdbfaeb882fcaf7</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Cloud &amp; DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>First Orion</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>North Little Rock, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, RDS, Databricks, Spark, CI/CD, CodeBuild, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53bbcc678b9b2126</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SDN Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>AIG GLOBAL OPERATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=924a8a8705d9e686</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SDN Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>AIG GLOBAL OPERATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07cd611e4010c8c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SDN Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>AIG GLOBAL OPERATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d9430066096f6a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SDN Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>AIG GLOBAL OPERATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e809e3665c70de7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>Senior Data &amp; AI Engineer</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Material Bank</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Boca Raton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a125832a9faf2b6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Material Bank</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13f4639de61892c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Material Bank</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D34" t="n">
         <v>10.4</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=aaf0998b173a8e22</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>jamf</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Jenkins, Git, Python</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=476d52c54642bad6</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – ClickHouse Infrastructure</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Bloomberg</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RDS, Spark, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d09956aa680bb5f9</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-01.xlsx
+++ b/results/job_matches_2026-06-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AWS Kinesis Developer – R01565561</t>
+          <t>Mid-Level Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Athena, S3, SQS, API Gateway, RDS, Scala, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Google Cloud Platform, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,19 +601,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b01bb5faaa172a</t>
+          <t>https://www.indeed.com/viewjob?jk=bd8003ebc53d5ab3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Healthcare Integration Engineer</t>
+          <t>DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Justhire Technology</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3653f445e14812b8</t>
+          <t>https://www.indeed.com/viewjob?jk=bde27c3a7c822c19</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>AWS Kinesis Developer – R01565561</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SmartTIX</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Google Cloud Platform</t>
+          <t>AWS, Lambda, Kinesis, Athena, S3, SQS, API Gateway, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a65fe6b467bcebd9</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b01bb5faaa172a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Edgewater Federal Solutions</t>
+          <t>SmartTIX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db0719f5d865d28c</t>
+          <t>https://www.indeed.com/viewjob?jk=a65fe6b467bcebd9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>DevOps &amp; Platform Engineer (AWS / CI/CD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Evolvers Group</t>
+          <t>Agilent Technologies</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8263a31ade65f67d</t>
+          <t>https://www.indeed.com/viewjob?jk=27d70a9322c9786b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Informatica Product Owner - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bar Harbor, ME, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, Step Functions, S3, HDFS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db23110a8baa26ec</t>
+          <t>https://www.indeed.com/viewjob?jk=2623aa90a431c062</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Informatica Product Owner - Remote</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Edgewater Federal Solutions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22eadc10f98f86e</t>
+          <t>https://www.indeed.com/viewjob?jk=db0719f5d865d28c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Informatica Product Owner - Remote</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, ECS, RDS, Vertex AI, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc73b585f3756066</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5b7f70487a08c4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Informatica Product Owner - Remote</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>The Evolvers Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Alachua, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=031cba0efbfb272c</t>
+          <t>https://www.indeed.com/viewjob?jk=8263a31ade65f67d</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Bar Harbor, ME, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356fb2d131354301</t>
+          <t>https://www.indeed.com/viewjob?jk=db23110a8baa26ec</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data &amp; AI Intern</t>
+          <t>Informatica Product Owner - Remote</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e70e856c1968e4a1</t>
+          <t>https://www.indeed.com/viewjob?jk=f22eadc10f98f86e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Informatica Product Owner - Remote</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SkySlope</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3139e590b6a0719</t>
+          <t>https://www.indeed.com/viewjob?jk=bc73b585f3756066</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Architect - C2H - Onsite</t>
+          <t>Informatica Product Owner - Remote</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Alachua, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b7749106eebc9f</t>
+          <t>https://www.indeed.com/viewjob?jk=031cba0efbfb272c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Informatica Product Owner - Remote</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>William Blair &amp; Company</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c04b4f9272c367</t>
+          <t>https://www.indeed.com/viewjob?jk=356fb2d131354301</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Solution Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b20eb19409e2893</t>
+          <t>https://www.indeed.com/viewjob?jk=a5ca6c0823ba9179</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer (Co-op)</t>
+          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ribbon Communications</t>
+          <t>MindCare Solutions Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Westford, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Hadoop, HDFS, Impala, Scala, Kafka, NoSQL, ETL</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a073e33a9128dc9</t>
+          <t>https://www.indeed.com/viewjob?jk=8e4a9a916464c719</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>MindCare Solutions Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3a65fdc259b09f3</t>
+          <t>https://www.indeed.com/viewjob?jk=d6c563ff6c6c61af</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Data &amp; AI Intern</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, ETL, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d60d1f21a4e182da</t>
+          <t>https://www.indeed.com/viewjob?jk=e70e856c1968e4a1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Software Engineer - Java</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Knott Cleaning</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d74fea61e0c268af</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a5aeeb93f9ed7b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>RWD Delivery Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Brotherhood Mutual Insurance Company</t>
+          <t>Norstella</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Cloud Storage, Scala, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae07d8ce5e9b6c72</t>
+          <t>https://www.indeed.com/viewjob?jk=480648c59cb92063</t>
         </is>
       </c>
     </row>
@@ -1278,20 +1278,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>SkySlope</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, S3, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55697a169692173b</t>
+          <t>https://www.indeed.com/viewjob?jk=d3139e590b6a0719</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Solutions Engineer(Python/Airflow)</t>
+          <t>Data Architect - C2H - Onsite</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EDB</t>
+          <t>TEEMA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebdbfaeb882fcaf7</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b7749106eebc9f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cloud &amp; DevOps Engineer</t>
+          <t>DevOps Engineer - Security / PCI and Compliance</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>First Orion</t>
+          <t>Edlio LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Databricks, Spark, CI/CD, CodeBuild, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,172 +1371,172 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53bbcc678b9b2126</t>
+          <t>https://www.indeed.com/viewjob?jk=324d5a4d0e21543e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SDN Automation Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AIG GLOBAL OPERATIONS, INC.</t>
+          <t>William Blair &amp; Company</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=924a8a8705d9e686</t>
+          <t>https://www.indeed.com/viewjob?jk=03c04b4f9272c367</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SDN Automation Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AIG GLOBAL OPERATIONS, INC.</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07cd611e4010c8c8</t>
+          <t>https://www.indeed.com/viewjob?jk=34260a70256866e8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SDN Automation Engineer</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AIG GLOBAL OPERATIONS, INC.</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d9430066096f6a2</t>
+          <t>https://www.indeed.com/viewjob?jk=6a382e3d5a9c0a8a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SDN Automation Engineer</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AIG GLOBAL OPERATIONS, INC.</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e809e3665c70de7d</t>
+          <t>https://www.indeed.com/viewjob?jk=ff7e9e84a12c3534</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Material Bank</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a125832a9faf2b6d</t>
+          <t>https://www.indeed.com/viewjob?jk=a75befce9107331c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Material Bank</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f4639de61892c3</t>
+          <t>https://www.indeed.com/viewjob?jk=14cc48e7f7f837c5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Material Bank</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,75 +1616,1475 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaf0998b173a8e22</t>
+          <t>https://www.indeed.com/viewjob?jk=2b20eb19409e2893</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Jenkins, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=476d52c54642bad6</t>
+          <t>https://www.indeed.com/viewjob?jk=c3a65fdc259b09f3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>Senior GCP Data Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>EXL Service</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RDS, GCP, BigQuery, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2564466ca73964ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=02afe5b9fb166a85</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Iselin, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e63d448fe3a8c008</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e29f217984e78bba</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Python Developer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, ETL, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d60d1f21a4e182da</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d74fea61e0c268af</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - International eKYC, Identity Graph</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, ELT, MLOps</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d9272c185c23e1a</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - International eKYC, Identity Graph</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, ELT, MLOps</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=580e242948a318a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - International eKYC, Identity Graph</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, ELT, MLOps</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d8c35a8039f2d699</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - International eKYC, Identity Graph</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, ELT, MLOps</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec4cb44123f0e681</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>L2 Application Support Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Barclays</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Whippany, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e03b026a5da4056</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Bass Pro Shops</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Springfield, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=150c1c460a8f2243</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>AL/ML Engineer / Azure Policy, AWS SCP</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Fustis LLC</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3a5d8cf56d01694</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b255f7cfbea2f42a</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21d42f664c1bc212</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b23576df86210e6a</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=268739eff36de340</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Epsilon</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, NoSQL</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55697a169692173b</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, ELT, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4ec0556f52ecfdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Brotherhood Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Fort Wayne, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ae07d8ce5e9b6c72</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer, AI Specialist</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, PostgreSQL, GitHub Actions, Terraform, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e0a0b45e1676a63</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior Software Developer - Retail Technology &amp; Platform Engineering</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Chrome Hearts</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Hollywood, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, PySpark, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bdd17c64ea657ee3</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>MuleSoft QA Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>UniFirst</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Wilmington, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fbe31b446b710556</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Full-Stack Data BI Engineer (on-site)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Ziosk</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Unity Catalog, BigQuery, Spark, Snowflake, Dimensional Modeling, Power BI, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83d0f91e0077746c</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Full-Stack Data BI Engineer (on-site)</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Ziosk</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Unity Catalog, BigQuery, Spark, Snowflake, Dimensional Modeling, Power BI, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd42e61b1f00ae70</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Solutions Engineer(Python/Airflow)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>EDB</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ebdbfaeb882fcaf7</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Cloud &amp; DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>First Orion</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>North Little Rock, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, RDS, Databricks, Spark, CI/CD, CodeBuild, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53bbcc678b9b2126</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>MuleSoft Developer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>UniFirst</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Wilmington, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a3430d97e76b325</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Lakebase Sales Specialist - Retail</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2fa83c7a2449f337</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SDN Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>AIG GLOBAL OPERATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=924a8a8705d9e686</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>SDN Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>AIG GLOBAL OPERATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07cd611e4010c8c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>SDN Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>AIG GLOBAL OPERATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d9430066096f6a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>SDN Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>AIG GLOBAL OPERATIONS, INC.</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e809e3665c70de7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Material Bank</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Boca Raton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a125832a9faf2b6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Material Bank</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13f4639de61892c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Material Bank</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aaf0998b173a8e22</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Application Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Applied Information Sciences</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>API Gateway, Azure, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91d2fa8b6f031cc8</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Senior GTM Data Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Global Payments</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Oklahoma City, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RDS, BigQuery, Scala, Snowflake, ELT, dbt, Power BI, Tableau, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=73a48857d65986eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>jamf</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Jenkins, Git, Python</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=476d52c54642bad6</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>DevOps Engineer-WO-003</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>SOSi</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ecd5f96e1434ab45</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>Senior Software Engineer – ClickHouse Infrastructure</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>Bloomberg</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>New York, NY, US USA</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D76" t="n">
         <v>10.4</v>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>RDS, Spark, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d09956aa680bb5f9</t>
         </is>
